--- a/Train_A_Skill/Level1_Skill_Vertical_BentArmPush_PikeElevatedHSPU.xlsx
+++ b/Train_A_Skill/Level1_Skill_Vertical_BentArmPush_PikeElevatedHSPU.xlsx
@@ -93,7 +93,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -117,6 +117,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFE599"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEAF6E1"/>
       </patternFill>
     </fill>
@@ -133,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -162,16 +167,19 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -539,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -599,22 +607,22 @@
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>○  0</t>
+          <t>○  1</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Seated Straddle 1 Arm OH Press</t>
+          <t>Eccentric Down Dog Push-up</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>10 reps each arm at 20% bodyweight</t>
+          <t>10 reps · head in line with hands, elbows flare on lowering</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 5–10% BW</t>
+          <t>6–10 reps</t>
         </is>
       </c>
     </row>
@@ -626,12 +634,12 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Seated Bench Overhead Press</t>
+          <t>Seated Straddle 1 Arm OH Press</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>10 reps each side at 20% bodyweight</t>
+          <t>10 reps each arm at 20% bodyweight</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -648,22 +656,44 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
+          <t>Seated Bench Overhead Press</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>10 reps each side at 20% bodyweight</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 5–10% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
           <t>BB Overhead Press</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>10 reps at 50% bodyweight</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>5–10 reps @ 15–30% BW</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D4:F4"/>
@@ -672,11 +702,13 @@
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D10:F10"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -689,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -754,12 +786,12 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Eccentric Down Dog Push-up</t>
+          <t>Down Dog Pushup</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>10 reps · head in line with hands, elbows flare on lowering</t>
+          <t>10 reps, head touching floor</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -776,39 +808,39 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Down Dog Pushup</t>
+          <t>Eccentric Pike Pushup</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>10 reps, head touching floor</t>
+          <t>15 reps, 3s eccentric lowering</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>6–10 reps</t>
+          <t>5–15 reps</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>○  2</t>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Eccentric Pike Pushup</t>
+          <t>Seated Straddle 1 Arm OH Press</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>15 reps, 3s eccentric lowering</t>
+          <t>10 reps each arm at 20% bodyweight</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>5–15 reps</t>
+          <t>5–10 reps @ 15% BW</t>
         </is>
       </c>
     </row>
@@ -820,12 +852,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Seated Straddle 1 Arm OH Press</t>
+          <t>Seated Bench Overhead Press</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>10 reps each arm at 20% bodyweight</t>
+          <t>10 reps each side at 20% bodyweight</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -842,50 +874,27 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Seated Bench Overhead Press</t>
+          <t>BB Overhead Press</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>10 reps each side at 20% bodyweight</t>
+          <t>10 reps at 50% bodyweight</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 15% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>BB Overhead Press</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>10 reps at 50% bodyweight</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
           <t>5–10 reps @ 35–40% BW</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="D12:F12"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="D7:F7"/>
@@ -898,7 +907,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -991,9 +999,9 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>○  4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1160,22 +1168,22 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>TEST: Pike Elevated HSPU</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PASS: 10 reps</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>4–10 reps · 2 sets  ✦</t>
         </is>
